--- a/templates/Application-Tracker-Pro-Sample.xlsx
+++ b/templates/Application-Tracker-Pro-Sample.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="279">
   <si>
     <t xml:space="preserve">ApplyAbroadLab.com — Application Tracker Pro</t>
   </si>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">▶  How It Works</t>
   </si>
   <si>
-    <t xml:space="preserve">Tip: update Status, Priority and Deadline in the Applications sheet — every KPI, chart and list on this page recalculates automatically.</t>
+    <t xml:space="preserve">Tip: every underlined number or name on this page is a link — one click opens the source row. If a linked cell is already selected, a second click enters edit mode; press Esc to leave it.</t>
   </si>
   <si>
     <t xml:space="preserve">CONNECT WITH APPLY ABROAD LAB</t>
@@ -181,6 +181,9 @@
     <t xml:space="preserve">Main tracker — edit the white columns. Grey columns (Country, Supervisor, Funding, Days Until Deadline) are calculated automatically.</t>
   </si>
   <si>
+    <t xml:space="preserve">◀ Back to Dashboard</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID</t>
   </si>
   <si>
@@ -781,6 +784,9 @@
     <t xml:space="preserve">Overall (average)</t>
   </si>
   <si>
+    <t xml:space="preserve">Open university record</t>
+  </si>
+  <si>
     <t xml:space="preserve">How It Works</t>
   </si>
   <si>
@@ -836,6 +842,12 @@
   </si>
   <si>
     <t xml:space="preserve">Deadlines are fixed dates. If you record later, shift a few deadlines into the next 30 days so the Upcoming Deadlines list and the red alerts are visible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation &amp; links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underlined numbers and names are links. One click on a link opens the source row (KPI cards and chart-data labels open the Applications sheet; deadline and Explorer rows open the exact application; Scoring and the Supervisor column open the university record). Every sheet has a Back to Dashboard link at the top right. Excel rule: if a linked cell is already the selected cell, clicking it again enters edit mode instead of following the link — press Esc, click any other cell, then click the link once.</t>
   </si>
   <si>
     <t xml:space="preserve">Built with</t>
@@ -866,7 +878,7 @@
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,6 +943,7 @@
     </font>
     <font>
       <b val="true"/>
+      <u val="single"/>
       <sz val="24"/>
       <color rgb="FF12213D"/>
       <name val="Arial"/>
@@ -939,8 +952,17 @@
     </font>
     <font>
       <b val="true"/>
+      <u val="single"/>
       <sz val="24"/>
       <color rgb="FF0E7C66"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="9"/>
+      <color rgb="FF5F5E5A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -964,6 +986,14 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="9"/>
+      <color rgb="FF1565C0"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -994,18 +1024,19 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <u val="single"/>
       <sz val="9"/>
       <color rgb="FF1565C0"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -1057,6 +1088,15 @@
       <b val="true"/>
       <sz val="16"/>
       <color rgb="FF12213D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF1565C0"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1143,7 +1183,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1184,59 +1224,147 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1244,76 +1372,24 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1325,7 +1401,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="30">
     <dxf>
       <font>
         <b val="1"/>
@@ -1372,6 +1448,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4F6FA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1565C0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2139,11 +2223,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17150109"/>
-        <c:axId val="62774939"/>
+        <c:axId val="9938779"/>
+        <c:axId val="35789540"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17150109"/>
+        <c:axId val="9938779"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2175,7 +2259,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62774939"/>
+        <c:crossAx val="35789540"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2183,7 +2267,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62774939"/>
+        <c:axId val="35789540"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2215,7 +2299,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17150109"/>
+        <c:crossAx val="9938779"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2677,11 +2761,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="86970096"/>
-        <c:axId val="45753562"/>
+        <c:axId val="11359523"/>
+        <c:axId val="46852421"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="86970096"/>
+        <c:axId val="11359523"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2710,7 +2794,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45753562"/>
+        <c:crossAx val="46852421"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2718,7 +2802,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45753562"/>
+        <c:axId val="46852421"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -2762,7 +2846,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86970096"/>
+        <c:crossAx val="11359523"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2966,11 +3050,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="14191603"/>
-        <c:axId val="9376048"/>
+        <c:axId val="79781119"/>
+        <c:axId val="87077005"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14191603"/>
+        <c:axId val="79781119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3002,7 +3086,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9376048"/>
+        <c:crossAx val="87077005"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3010,7 +3094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9376048"/>
+        <c:axId val="87077005"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3052,7 +3136,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14191603"/>
+        <c:crossAx val="79781119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3548,11 +3632,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="49765161"/>
-        <c:axId val="48438402"/>
+        <c:axId val="55289646"/>
+        <c:axId val="48113344"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="49765161"/>
+        <c:axId val="55289646"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -3581,7 +3665,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48438402"/>
+        <c:crossAx val="48113344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3589,7 +3673,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48438402"/>
+        <c:axId val="48113344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -3633,7 +3717,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49765161"/>
+        <c:crossAx val="55289646"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3825,14 +3909,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>78120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>981720</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>57960</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>58320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3840,7 +3924,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="2876400"/>
+        <a:off x="0" y="3067200"/>
         <a:ext cx="6479640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -4079,7 +4163,7 @@
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="str">
         <f aca="true">"Command center for a graduate application campaign  |  Last updated: "&amp;TEXT(TODAY(),"dd-mmm-yyyy")</f>
-        <v>Command center for a graduate application campaign  |  Last updated: 21-Sep-2026</v>
+        <v>Command center for a graduate application campaign  |  Last updated: 22-Sep-2026</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -4138,7 +4222,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="8" t="n">
         <f aca="false">SUMPRODUCT(MIN(IF(Applications!$I$4:$I$23&gt;=0,Applications!$I$4:$I$23)))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="7" t="n">
@@ -4161,7 +4245,7 @@
         <v>7.7</v>
       </c>
       <c r="M6" s="7"/>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="P6" s="6" t="n">
@@ -4170,7 +4254,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="P7" s="6" t="n">
@@ -4179,25 +4263,25 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10" t="s">
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="O8" s="6" t="s">
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="O8" s="10" t="s">
         <v>16</v>
       </c>
       <c r="P8" s="6" t="n">
@@ -4206,7 +4290,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="10" t="s">
         <v>17</v>
       </c>
       <c r="P9" s="6" t="n">
@@ -4215,7 +4299,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O10" s="6" t="s">
+      <c r="O10" s="10" t="s">
         <v>18</v>
       </c>
       <c r="P10" s="6" t="n">
@@ -4224,7 +4308,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O11" s="6" t="s">
+      <c r="O11" s="10" t="s">
         <v>19</v>
       </c>
       <c r="P11" s="6" t="n">
@@ -4245,7 +4329,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O14" s="6" t="s">
+      <c r="O14" s="10" t="s">
         <v>21</v>
       </c>
       <c r="P14" s="6" t="n">
@@ -4254,7 +4338,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O15" s="6" t="s">
+      <c r="O15" s="10" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6" t="n">
@@ -4263,7 +4347,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O16" s="6" t="s">
+      <c r="O16" s="10" t="s">
         <v>23</v>
       </c>
       <c r="P16" s="6" t="n">
@@ -4272,7 +4356,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O17" s="6" t="s">
+      <c r="O17" s="10" t="s">
         <v>24</v>
       </c>
       <c r="P17" s="6" t="n">
@@ -4281,7 +4365,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O18" s="6" t="s">
+      <c r="O18" s="10" t="s">
         <v>25</v>
       </c>
       <c r="P18" s="6" t="n">
@@ -4290,7 +4374,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O19" s="6" t="s">
+      <c r="O19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P19" s="6" t="n">
@@ -4299,7 +4383,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O20" s="6" t="s">
+      <c r="O20" s="10" t="s">
         <v>27</v>
       </c>
       <c r="P20" s="6" t="n">
@@ -4308,7 +4392,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O21" s="6" t="s">
+      <c r="O21" s="10" t="s">
         <v>28</v>
       </c>
       <c r="P21" s="6" t="n">
@@ -4321,284 +4405,284 @@
       <c r="P22" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="I27" s="11" t="s">
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="I27" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13" t="s">
+      <c r="D28" s="14"/>
+      <c r="E28" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="12" t="s">
+      <c r="F28" s="14"/>
+      <c r="G28" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="15" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,1),Applications!$Q$4:$Q$23,0)),"")</f>
+      <c r="C29" s="16" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH(SMALL(Applications!$Q$4:$Q$23,1),Applications!$Q$4:$Q$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,1),Applications!$Q$4:$Q$23,0))),"")</f>
         <v>Technical University of Munich</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15" t="str">
+      <c r="D29" s="16"/>
+      <c r="E29" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH(SMALL(Applications!$Q$4:$Q$23,1),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>PhD in Computational Biology</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16" t="n">
+      <c r="F29" s="17"/>
+      <c r="G29" s="18" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH(SMALL(Applications!$Q$4:$Q$23,1),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>46300</v>
       </c>
-      <c r="H29" s="17" t="n">
+      <c r="H29" s="19" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH(SMALL(Applications!$Q$4:$Q$23,1),Applications!$Q$4:$Q$23,0)),"")</f>
-        <v>14</v>
-      </c>
-      <c r="I29" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="15" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,2),Applications!$Q$4:$Q$23,0)),"")</f>
+      <c r="C30" s="16" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH(SMALL(Applications!$Q$4:$Q$23,2),Applications!$Q$4:$Q$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,2),Applications!$Q$4:$Q$23,0))),"")</f>
         <v>Delft University of Technology</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15" t="str">
+      <c r="D30" s="16"/>
+      <c r="E30" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH(SMALL(Applications!$Q$4:$Q$23,2),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>PhD in Structural Engineering</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16" t="n">
+      <c r="F30" s="17"/>
+      <c r="G30" s="18" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH(SMALL(Applications!$Q$4:$Q$23,2),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>46307</v>
       </c>
-      <c r="H30" s="17" t="n">
+      <c r="H30" s="19" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH(SMALL(Applications!$Q$4:$Q$23,2),Applications!$Q$4:$Q$23,0)),"")</f>
-        <v>21</v>
-      </c>
-      <c r="I30" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="15" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,3),Applications!$Q$4:$Q$23,0)),"")</f>
+      <c r="C31" s="16" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH(SMALL(Applications!$Q$4:$Q$23,3),Applications!$Q$4:$Q$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,3),Applications!$Q$4:$Q$23,0))),"")</f>
         <v>University of Amsterdam</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15" t="str">
+      <c r="D31" s="16"/>
+      <c r="E31" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH(SMALL(Applications!$Q$4:$Q$23,3),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>PhD in Clinical Psychology</v>
       </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="16" t="n">
+      <c r="F31" s="17"/>
+      <c r="G31" s="18" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH(SMALL(Applications!$Q$4:$Q$23,3),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>46313</v>
       </c>
-      <c r="H31" s="17" t="n">
+      <c r="H31" s="19" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH(SMALL(Applications!$Q$4:$Q$23,3),Applications!$Q$4:$Q$23,0)),"")</f>
-        <v>27</v>
-      </c>
-      <c r="I31" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="15" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,4),Applications!$Q$4:$Q$23,0)),"")</f>
+      <c r="C32" s="16" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH(SMALL(Applications!$Q$4:$Q$23,4),Applications!$Q$4:$Q$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,4),Applications!$Q$4:$Q$23,0))),"")</f>
         <v>Karolinska Institutet</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15" t="str">
+      <c r="D32" s="16"/>
+      <c r="E32" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH(SMALL(Applications!$Q$4:$Q$23,4),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>Postdoc in Cancer Biology</v>
       </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="16" t="n">
+      <c r="F32" s="17"/>
+      <c r="G32" s="18" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH(SMALL(Applications!$Q$4:$Q$23,4),Applications!$Q$4:$Q$23,0)),"")</f>
         <v>46315</v>
       </c>
-      <c r="H32" s="17" t="n">
+      <c r="H32" s="19" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH(SMALL(Applications!$Q$4:$Q$23,4),Applications!$Q$4:$Q$23,0)),"")</f>
-        <v>29</v>
-      </c>
-      <c r="I32" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C33" s="15" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,5),Applications!$Q$4:$Q$23,0)),"")</f>
+      <c r="C33" s="16" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH(SMALL(Applications!$Q$4:$Q$23,5),Applications!$Q$4:$Q$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,5),Applications!$Q$4:$Q$23,0))),"")</f>
         <v/>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15" t="str">
+      <c r="D33" s="16"/>
+      <c r="E33" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH(SMALL(Applications!$Q$4:$Q$23,5),Applications!$Q$4:$Q$23,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16" t="str">
+      <c r="F33" s="17"/>
+      <c r="G33" s="18" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH(SMALL(Applications!$Q$4:$Q$23,5),Applications!$Q$4:$Q$23,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="17" t="str">
+      <c r="H33" s="19" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH(SMALL(Applications!$Q$4:$Q$23,5),Applications!$Q$4:$Q$23,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18" t="s">
+      <c r="I33" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C34" s="15" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,6),Applications!$Q$4:$Q$23,0)),"")</f>
+      <c r="C34" s="16" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH(SMALL(Applications!$Q$4:$Q$23,6),Applications!$Q$4:$Q$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH(SMALL(Applications!$Q$4:$Q$23,6),Applications!$Q$4:$Q$23,0))),"")</f>
         <v/>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15" t="str">
+      <c r="D34" s="16"/>
+      <c r="E34" s="17" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH(SMALL(Applications!$Q$4:$Q$23,6),Applications!$Q$4:$Q$23,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="16" t="str">
+      <c r="F34" s="17"/>
+      <c r="G34" s="18" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH(SMALL(Applications!$Q$4:$Q$23,6),Applications!$Q$4:$Q$23,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="17" t="str">
+      <c r="H34" s="19" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH(SMALL(Applications!$Q$4:$Q$23,6),Applications!$Q$4:$Q$23,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -4660,13 +4744,33 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="ApplyAbroadLab.com — Application Tracker Pro"/>
-    <hyperlink ref="I29" r:id="rId2" location="'Applications'!A1" display="▶  Applications"/>
-    <hyperlink ref="I30" r:id="rId3" location="'Universities%20&amp;%20Supervisors'!A1" display="▶  Universities &amp; Supervisors"/>
-    <hyperlink ref="I31" r:id="rId4" location="'Explorer'!A1" display="▶  Explorer (interactive filter)"/>
-    <hyperlink ref="I32" r:id="rId5" location="'Scoring'!A1" display="▶  Scoring (radar inputs)"/>
-    <hyperlink ref="I33" r:id="rId6" location="'How%20It%20Works'!A1" display="▶  How It Works"/>
-    <hyperlink ref="C39" r:id="rId7" display="https://applyabroadlab.com/"/>
-    <hyperlink ref="C40" r:id="rId8" display="Apply Abroad Lab"/>
+    <hyperlink ref="B6" r:id="rId2" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Apply%20Abroad%20Lab%20Application%20Tracker%20Pro.xlsx#'Applications'!A4"/>
+    <hyperlink ref="D6" r:id="rId3" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Apply%20Abroad%20Lab%20Application%20Tracker%20Pro.xlsx#'Applications'!A4"/>
+    <hyperlink ref="F6" r:id="rId4" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Apply%20Abroad%20Lab%20Application%20Tracker%20Pro.xlsx#'Applications'!A4"/>
+    <hyperlink ref="H6" r:id="rId5" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Apply%20Abroad%20Lab%20Application%20Tracker%20Pro.xlsx#'Applications'!A4"/>
+    <hyperlink ref="J6" r:id="rId6" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Apply%20Abroad%20Lab%20Application%20Tracker%20Pro.xlsx#'Applications'!A4"/>
+    <hyperlink ref="L6" r:id="rId7" location="'Applications'!A4" display="file:///mnt/user-data/outputs/Apply%20Abroad%20Lab%20Application%20Tracker%20Pro.xlsx#'Applications'!A4"/>
+    <hyperlink ref="O6" r:id="rId8" location="'Applications'!J4" display="Not Started"/>
+    <hyperlink ref="O7" r:id="rId9" location="'Applications'!J4" display="In Progress"/>
+    <hyperlink ref="O8" r:id="rId10" location="'Applications'!J4" display="Submitted"/>
+    <hyperlink ref="O9" r:id="rId11" location="'Applications'!J4" display="Interview"/>
+    <hyperlink ref="O10" r:id="rId12" location="'Applications'!J4" display="Accepted"/>
+    <hyperlink ref="O11" r:id="rId13" location="'Applications'!J4" display="Rejected"/>
+    <hyperlink ref="O14" r:id="rId14" location="'Applications'!C4" display="Belgium"/>
+    <hyperlink ref="O15" r:id="rId15" location="'Applications'!C4" display="Canada"/>
+    <hyperlink ref="O16" r:id="rId16" location="'Applications'!C4" display="Germany"/>
+    <hyperlink ref="O17" r:id="rId17" location="'Applications'!C4" display="Italy"/>
+    <hyperlink ref="O18" r:id="rId18" location="'Applications'!C4" display="Netherlands"/>
+    <hyperlink ref="O19" r:id="rId19" location="'Applications'!C4" display="Norway"/>
+    <hyperlink ref="O20" r:id="rId20" location="'Applications'!C4" display="Sweden"/>
+    <hyperlink ref="O21" r:id="rId21" location="'Applications'!C4" display="Switzerland"/>
+    <hyperlink ref="I29" r:id="rId22" location="'Applications'!A1" display="▶  Applications"/>
+    <hyperlink ref="I30" r:id="rId23" location="'Universities%20&amp;%20Supervisors'!A1" display="▶  Universities &amp; Supervisors"/>
+    <hyperlink ref="I31" r:id="rId24" location="'Explorer'!A1" display="▶  Explorer (interactive filter)"/>
+    <hyperlink ref="I32" r:id="rId25" location="'Scoring'!A1" display="▶  Scoring (radar inputs)"/>
+    <hyperlink ref="I33" r:id="rId26" location="'How%20It%20Works'!A1" display="▶  How It Works"/>
+    <hyperlink ref="C39" r:id="rId27" display="https://applyabroadlab.com/"/>
+    <hyperlink ref="C40" r:id="rId28" display="Apply Abroad Lab"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4675,7 +4779,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId9"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
 
@@ -4727,1349 +4831,1352 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="23" t="s">
+      <c r="E3" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="G3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="23" t="s">
+      <c r="I3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="23" t="s">
+      <c r="K3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="L3" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="M3" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="O3" s="23" t="s">
+      <c r="N3" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="O3" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="P3" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="Q3" s="26" t="s">
         <v>62</v>
       </c>
+      <c r="R3" s="26" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="n">
+      <c r="A4" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="25" t="str">
+      <c r="B4" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Germany</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="24" t="s">
+      <c r="D4" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="E4" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="F4" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B4,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B4,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Lena Hartmann</v>
       </c>
-      <c r="H4" s="27" t="n">
+      <c r="H4" s="31" t="n">
         <v>46300</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="I4" s="32" t="n">
         <f aca="true">IF(H4="","",H4-TODAY())</f>
-        <v>14</v>
-      </c>
-      <c r="J4" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L4" s="24" t="n">
+      <c r="K4" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M4" s="25" t="str">
+      <c r="M4" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (DFG)</v>
       </c>
-      <c r="N4" s="29" t="n">
+      <c r="N4" s="33" t="n">
         <v>0.8</v>
       </c>
-      <c r="O4" s="27" t="n">
+      <c r="O4" s="31" t="n">
         <v>46280</v>
       </c>
-      <c r="P4" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" s="24" t="n">
+      <c r="P4" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="27" t="n">
         <f aca="false">IF(AND(I4&lt;&gt;"",I4&gt;=0,I4&lt;=30),I4+ROW()/100000,"")</f>
-        <v>14.00004</v>
-      </c>
-      <c r="R4" s="24" t="n">
+        <v>13.00004</v>
+      </c>
+      <c r="R4" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C4=Explorer!$C$4),OR(Explorer!$C$5="All",J4=Explorer!$C$5),OR(Explorer!$C$6="All",K4=Explorer!$C$6)),MAX($R$3:R3)+1,"")</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="25" t="str">
+      <c r="B5" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B5,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Germany</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B5,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E5" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B5,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B5,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Jonas Weber</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="31" t="n">
         <v>46341</v>
       </c>
-      <c r="I5" s="28" t="n">
+      <c r="I5" s="32" t="n">
         <f aca="true">IF(H5="","",H5-TODAY())</f>
-        <v>55</v>
-      </c>
-      <c r="J5" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5" s="24" t="n">
+      <c r="K5" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="25" t="str">
+      <c r="M5" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B5,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (DKFZ)</v>
       </c>
-      <c r="N5" s="29" t="n">
+      <c r="N5" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="O5" s="27" t="n">
+      <c r="O5" s="31" t="n">
         <v>46275</v>
       </c>
-      <c r="P5" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q5" s="24" t="str">
+      <c r="P5" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" s="27" t="str">
         <f aca="false">IF(AND(I5&lt;&gt;"",I5&gt;=0,I5&lt;=30),I5+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R5" s="24" t="n">
+      <c r="R5" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C5=Explorer!$C$4),OR(Explorer!$C$5="All",J5=Explorer!$C$5),OR(Explorer!$C$6="All",K5=Explorer!$C$6)),MAX($R$3:R4)+1,"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="n">
+      <c r="A6" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="25" t="str">
+      <c r="B6" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B6,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Germany</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="24" t="s">
+      <c r="D6" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="F6" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B6,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E6" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B6,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B6,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Katrin Vogel</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="31" t="n">
         <v>46418</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="32" t="n">
         <f aca="true">IF(H6="","",H6-TODAY())</f>
-        <v>132</v>
-      </c>
-      <c r="J6" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="J6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L6" s="24" t="n">
+      <c r="K6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M6" s="25" t="str">
+      <c r="M6" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B6,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (Institute)</v>
       </c>
-      <c r="N6" s="29" t="n">
+      <c r="N6" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="O6" s="27"/>
-      <c r="P6" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q6" s="24" t="str">
+      <c r="O6" s="31"/>
+      <c r="P6" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q6" s="27" t="str">
         <f aca="false">IF(AND(I6&lt;&gt;"",I6&gt;=0,I6&lt;=30),I6+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R6" s="24" t="n">
+      <c r="R6" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C6=Explorer!$C$4),OR(Explorer!$C$5="All",J6=Explorer!$C$5),OR(Explorer!$C$6="All",K6=Explorer!$C$6)),MAX($R$3:R5)+1,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="25" t="str">
+      <c r="B7" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B7,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="24" t="s">
+      <c r="D7" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B7,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E7" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B7,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B7,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Pieter de Vries</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="31" t="n">
         <v>46307</v>
       </c>
-      <c r="I7" s="28" t="n">
+      <c r="I7" s="32" t="n">
         <f aca="true">IF(H7="","",H7-TODAY())</f>
-        <v>21</v>
-      </c>
-      <c r="J7" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L7" s="24" t="n">
+      <c r="K7" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M7" s="25" t="str">
+      <c r="M7" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B7,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (University)</v>
       </c>
-      <c r="N7" s="29" t="n">
+      <c r="N7" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="27" t="n">
+      <c r="O7" s="31" t="n">
         <v>46267</v>
       </c>
-      <c r="P7" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q7" s="24" t="n">
+      <c r="P7" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q7" s="27" t="n">
         <f aca="false">IF(AND(I7&lt;&gt;"",I7&gt;=0,I7&lt;=30),I7+ROW()/100000,"")</f>
-        <v>21.00007</v>
-      </c>
-      <c r="R7" s="24" t="n">
+        <v>20.00007</v>
+      </c>
+      <c r="R7" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C7=Explorer!$C$4),OR(Explorer!$C$5="All",J7=Explorer!$C$5),OR(Explorer!$C$6="All",K7=Explorer!$C$6)),MAX($R$3:R6)+1,"")</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="n">
+      <c r="A8" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="25" t="str">
+      <c r="B8" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B8,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="24" t="s">
+      <c r="D8" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B8,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E8" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B8,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B8,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Sanne Bakker</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="31" t="n">
         <v>46313</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="32" t="n">
         <f aca="true">IF(H8="","",H8-TODAY())</f>
-        <v>27</v>
-      </c>
-      <c r="J8" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="24" t="n">
+      <c r="K8" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="25" t="str">
+      <c r="M8" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B8,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (NWO)</v>
       </c>
-      <c r="N8" s="29" t="n">
+      <c r="N8" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O8" s="27" t="n">
+      <c r="O8" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="P8" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q8" s="24" t="n">
+      <c r="P8" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" s="27" t="n">
         <f aca="false">IF(AND(I8&lt;&gt;"",I8&gt;=0,I8&lt;=30),I8+ROW()/100000,"")</f>
-        <v>27.00008</v>
-      </c>
-      <c r="R8" s="24" t="n">
+        <v>26.00008</v>
+      </c>
+      <c r="R8" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C8=Explorer!$C$4),OR(Explorer!$C$5="All",J8=Explorer!$C$5),OR(Explorer!$C$6="All",K8=Explorer!$C$6)),MAX($R$3:R7)+1,"")</f>
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="25" t="str">
+      <c r="B9" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B9,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="24" t="s">
+      <c r="D9" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B9,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E9" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B9,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B9,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Joris van Dijk</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="31" t="n">
         <v>46357</v>
       </c>
-      <c r="I9" s="28" t="n">
+      <c r="I9" s="32" t="n">
         <f aca="true">IF(H9="","",H9-TODAY())</f>
-        <v>71</v>
-      </c>
-      <c r="J9" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L9" s="24" t="n">
+      <c r="K9" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M9" s="25" t="str">
+      <c r="M9" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B9,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (University)</v>
       </c>
-      <c r="N9" s="29" t="n">
+      <c r="N9" s="33" t="n">
         <v>0.7</v>
       </c>
-      <c r="O9" s="27" t="n">
+      <c r="O9" s="31" t="n">
         <v>46277</v>
       </c>
-      <c r="P9" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q9" s="24" t="str">
+      <c r="P9" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q9" s="27" t="str">
         <f aca="false">IF(AND(I9&lt;&gt;"",I9&gt;=0,I9&lt;=30),I9+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R9" s="24" t="n">
+      <c r="R9" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C9=Explorer!$C$4),OR(Explorer!$C$5="All",J9=Explorer!$C$5),OR(Explorer!$C$6="All",K9=Explorer!$C$6)),MAX($R$3:R8)+1,"")</f>
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="n">
+      <c r="A10" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="25" t="str">
+      <c r="B10" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B10,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="24" t="s">
+      <c r="D10" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B10,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E10" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B10,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B10,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Femke Jansen</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="31" t="n">
         <v>46371</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="32" t="n">
         <f aca="true">IF(H10="","",H10-TODAY())</f>
-        <v>85</v>
-      </c>
-      <c r="J10" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="L10" s="24" t="n">
+      <c r="K10" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M10" s="25" t="str">
+      <c r="M10" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B10,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (University)</v>
       </c>
-      <c r="N10" s="29" t="n">
+      <c r="N10" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="O10" s="27"/>
-      <c r="P10" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q10" s="24" t="str">
+      <c r="O10" s="31"/>
+      <c r="P10" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q10" s="27" t="str">
         <f aca="false">IF(AND(I10&lt;&gt;"",I10&gt;=0,I10&lt;=30),I10+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R10" s="24" t="n">
+      <c r="R10" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C10=Explorer!$C$4),OR(Explorer!$C$5="All",J10=Explorer!$C$5),OR(Explorer!$C$6="All",K10=Explorer!$C$6)),MAX($R$3:R9)+1,"")</f>
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="25" t="str">
+      <c r="B11" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B11,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Sweden</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="24" t="s">
+      <c r="D11" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="E11" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B11,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="F11" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B11,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B11,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Anna Lindqvist</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="31" t="n">
         <v>46315</v>
       </c>
-      <c r="I11" s="28" t="n">
+      <c r="I11" s="32" t="n">
         <f aca="true">IF(H11="","",H11-TODAY())</f>
-        <v>29</v>
-      </c>
-      <c r="J11" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11" s="24" t="n">
+      <c r="K11" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M11" s="25" t="str">
+      <c r="M11" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B11,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (KI)</v>
       </c>
-      <c r="N11" s="29" t="n">
+      <c r="N11" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O11" s="27" t="n">
+      <c r="O11" s="31" t="n">
         <v>46270</v>
       </c>
-      <c r="P11" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q11" s="24" t="n">
+      <c r="P11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="27" t="n">
         <f aca="false">IF(AND(I11&lt;&gt;"",I11&gt;=0,I11&lt;=30),I11+ROW()/100000,"")</f>
-        <v>29.00011</v>
-      </c>
-      <c r="R11" s="24" t="n">
+        <v>28.00011</v>
+      </c>
+      <c r="R11" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C11=Explorer!$C$4),OR(Explorer!$C$5="All",J11=Explorer!$C$5),OR(Explorer!$C$6="All",K11=Explorer!$C$6)),MAX($R$3:R10)+1,"")</f>
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="n">
+      <c r="A12" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="25" t="str">
+      <c r="B12" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B12,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Sweden</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="24" t="s">
+      <c r="D12" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B12,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E12" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B12,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B12,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Erik Johansson</v>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="31" t="n">
         <v>46356</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="32" t="n">
         <f aca="true">IF(H12="","",H12-TODAY())</f>
-        <v>70</v>
-      </c>
-      <c r="J12" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K12" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" s="24" t="n">
+      <c r="K12" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M12" s="25" t="str">
+      <c r="M12" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B12,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (WASP)</v>
       </c>
-      <c r="N12" s="29" t="n">
+      <c r="N12" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="O12" s="27" t="n">
+      <c r="O12" s="31" t="n">
         <v>46273</v>
       </c>
-      <c r="P12" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q12" s="24" t="str">
+      <c r="P12" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="27" t="str">
         <f aca="false">IF(AND(I12&lt;&gt;"",I12&gt;=0,I12&lt;=30),I12+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R12" s="24" t="n">
+      <c r="R12" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C12=Explorer!$C$4),OR(Explorer!$C$5="All",J12=Explorer!$C$5),OR(Explorer!$C$6="All",K12=Explorer!$C$6)),MAX($R$3:R11)+1,"")</f>
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="25" t="str">
+      <c r="B13" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B13,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Sweden</v>
       </c>
-      <c r="D13" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="24" t="s">
+      <c r="D13" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F13" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B13,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E13" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B13,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B13,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Karin Svensson</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="31" t="n">
         <v>46402</v>
       </c>
-      <c r="I13" s="28" t="n">
+      <c r="I13" s="32" t="n">
         <f aca="true">IF(H13="","",H13-TODAY())</f>
-        <v>116</v>
-      </c>
-      <c r="J13" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="J13" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L13" s="24" t="n">
+      <c r="K13" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M13" s="25" t="str">
+      <c r="M13" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B13,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (University)</v>
       </c>
-      <c r="N13" s="29" t="n">
+      <c r="N13" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="O13" s="27" t="n">
+      <c r="O13" s="31" t="n">
         <v>46266</v>
       </c>
-      <c r="P13" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q13" s="24" t="str">
+      <c r="P13" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q13" s="27" t="str">
         <f aca="false">IF(AND(I13&lt;&gt;"",I13&gt;=0,I13&lt;=30),I13+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R13" s="24" t="n">
+      <c r="R13" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C13=Explorer!$C$4),OR(Explorer!$C$5="All",J13=Explorer!$C$5),OR(Explorer!$C$6="All",K13=Explorer!$C$6)),MAX($R$3:R12)+1,"")</f>
         <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="25" t="str">
+      <c r="B14" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B14,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Italy</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="24" t="s">
+      <c r="D14" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="F14" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B14,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E14" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B14,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B14,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Giulia Ferrari</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="31" t="n">
         <v>46446</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="I14" s="32" t="n">
         <f aca="true">IF(H14="","",H14-TODAY())</f>
-        <v>160</v>
-      </c>
-      <c r="J14" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="J14" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="L14" s="24" t="n">
+      <c r="K14" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M14" s="25" t="str">
+      <c r="M14" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B14,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Scholarship (Regional)</v>
       </c>
-      <c r="N14" s="29" t="n">
+      <c r="N14" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="27"/>
-      <c r="P14" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q14" s="24" t="str">
+      <c r="O14" s="31"/>
+      <c r="P14" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q14" s="27" t="str">
         <f aca="false">IF(AND(I14&lt;&gt;"",I14&gt;=0,I14&lt;=30),I14+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R14" s="24" t="n">
+      <c r="R14" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C14=Explorer!$C$4),OR(Explorer!$C$5="All",J14=Explorer!$C$5),OR(Explorer!$C$6="All",K14=Explorer!$C$6)),MAX($R$3:R13)+1,"")</f>
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="25" t="str">
+      <c r="B15" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B15,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Italy</v>
       </c>
-      <c r="D15" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="24" t="s">
+      <c r="D15" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B15,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E15" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B15,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B15,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Marco Rossi</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="31" t="n">
         <v>46461</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="32" t="n">
         <f aca="true">IF(H15="","",H15-TODAY())</f>
-        <v>175</v>
-      </c>
-      <c r="J15" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="J15" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15" s="24" t="n">
+      <c r="K15" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L15" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M15" s="25" t="str">
+      <c r="M15" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B15,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Scholarship (University)</v>
       </c>
-      <c r="N15" s="29" t="n">
+      <c r="N15" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="O15" s="27" t="n">
+      <c r="O15" s="31" t="n">
         <v>46262</v>
       </c>
-      <c r="P15" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q15" s="24" t="str">
+      <c r="P15" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q15" s="27" t="str">
         <f aca="false">IF(AND(I15&lt;&gt;"",I15&gt;=0,I15&lt;=30),I15+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R15" s="24" t="n">
+      <c r="R15" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C15=Explorer!$C$4),OR(Explorer!$C$5="All",J15=Explorer!$C$5),OR(Explorer!$C$6="All",K15=Explorer!$C$6)),MAX($R$3:R14)+1,"")</f>
         <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="25" t="str">
+      <c r="B16" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B16,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Belgium</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B16,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="D16" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B16,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B16,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Bram Peeters</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="31" t="n">
         <v>46336</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I16" s="32" t="n">
         <f aca="true">IF(H16="","",H16-TODAY())</f>
-        <v>50</v>
-      </c>
-      <c r="J16" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" s="24" t="n">
+      <c r="K16" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M16" s="25" t="str">
+      <c r="M16" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B16,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (FWO)</v>
       </c>
-      <c r="N16" s="29" t="n">
+      <c r="N16" s="33" t="n">
         <v>0.65</v>
       </c>
-      <c r="O16" s="27" t="n">
+      <c r="O16" s="31" t="n">
         <v>46279</v>
       </c>
-      <c r="P16" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q16" s="24" t="str">
+      <c r="P16" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q16" s="27" t="str">
         <f aca="false">IF(AND(I16&lt;&gt;"",I16&gt;=0,I16&lt;=30),I16+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R16" s="24" t="n">
+      <c r="R16" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C16=Explorer!$C$4),OR(Explorer!$C$5="All",J16=Explorer!$C$5),OR(Explorer!$C$6="All",K16=Explorer!$C$6)),MAX($R$3:R15)+1,"")</f>
         <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="25" t="str">
+      <c r="B17" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B17,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Belgium</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B17,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="D17" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B17,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B17,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Elise Claes</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="31" t="n">
         <v>46376</v>
       </c>
-      <c r="I17" s="28" t="n">
+      <c r="I17" s="32" t="n">
         <f aca="true">IF(H17="","",H17-TODAY())</f>
-        <v>90</v>
-      </c>
-      <c r="J17" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="J17" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L17" s="24" t="n">
+      <c r="K17" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L17" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M17" s="25" t="str">
+      <c r="M17" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B17,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (BOF)</v>
       </c>
-      <c r="N17" s="29" t="n">
+      <c r="N17" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="27" t="n">
+      <c r="O17" s="31" t="n">
         <v>46268</v>
       </c>
-      <c r="P17" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q17" s="24" t="str">
+      <c r="P17" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q17" s="27" t="str">
         <f aca="false">IF(AND(I17&lt;&gt;"",I17&gt;=0,I17&lt;=30),I17+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R17" s="24" t="n">
+      <c r="R17" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C17=Explorer!$C$4),OR(Explorer!$C$5="All",J17=Explorer!$C$5),OR(Explorer!$C$6="All",K17=Explorer!$C$6)),MAX($R$3:R16)+1,"")</f>
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="25" t="str">
+      <c r="B18" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B18,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Switzerland</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B18,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="D18" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B18,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B18,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Daniel Meier</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="31" t="n">
         <v>46366</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="I18" s="32" t="n">
         <f aca="true">IF(H18="","",H18-TODAY())</f>
-        <v>80</v>
-      </c>
-      <c r="J18" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L18" s="24" t="n">
+      <c r="K18" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M18" s="25" t="str">
+      <c r="M18" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B18,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (ETH)</v>
       </c>
-      <c r="N18" s="29" t="n">
+      <c r="N18" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="O18" s="27"/>
-      <c r="P18" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q18" s="24" t="str">
+      <c r="O18" s="31"/>
+      <c r="P18" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q18" s="27" t="str">
         <f aca="false">IF(AND(I18&lt;&gt;"",I18&gt;=0,I18&lt;=30),I18+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R18" s="24" t="n">
+      <c r="R18" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C18=Explorer!$C$4),OR(Explorer!$C$5="All",J18=Explorer!$C$5),OR(Explorer!$C$6="All",K18=Explorer!$C$6)),MAX($R$3:R17)+1,"")</f>
         <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="25" t="str">
+      <c r="B19" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B19,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Switzerland</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B19,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="D19" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B19,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B19,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Claire Dubois</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="31" t="n">
         <v>46407</v>
       </c>
-      <c r="I19" s="28" t="n">
+      <c r="I19" s="32" t="n">
         <f aca="true">IF(H19="","",H19-TODAY())</f>
-        <v>121</v>
-      </c>
-      <c r="J19" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L19" s="24" t="n">
+      <c r="K19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M19" s="25" t="str">
+      <c r="M19" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B19,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (SNSF)</v>
       </c>
-      <c r="N19" s="29" t="n">
+      <c r="N19" s="33" t="n">
         <v>0.45</v>
       </c>
-      <c r="O19" s="27" t="n">
+      <c r="O19" s="31" t="n">
         <v>46274</v>
       </c>
-      <c r="P19" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q19" s="24" t="str">
+      <c r="P19" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q19" s="27" t="str">
         <f aca="false">IF(AND(I19&lt;&gt;"",I19&gt;=0,I19&lt;=30),I19+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R19" s="24" t="n">
+      <c r="R19" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C19=Explorer!$C$4),OR(Explorer!$C$5="All",J19=Explorer!$C$5),OR(Explorer!$C$6="All",K19=Explorer!$C$6)),MAX($R$3:R18)+1,"")</f>
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="C20" s="25" t="str">
+      <c r="B20" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B20,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Norway</v>
       </c>
-      <c r="D20" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B20,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="D20" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B20,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B20,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Ola Nilsen</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="31" t="n">
         <v>46351</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="I20" s="32" t="n">
         <f aca="true">IF(H20="","",H20-TODAY())</f>
-        <v>65</v>
-      </c>
-      <c r="J20" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="K20" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="L20" s="24" t="n">
+      <c r="K20" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M20" s="25" t="str">
+      <c r="M20" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B20,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (University)</v>
       </c>
-      <c r="N20" s="29" t="n">
+      <c r="N20" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O20" s="27" t="n">
+      <c r="O20" s="31" t="n">
         <v>46282</v>
       </c>
-      <c r="P20" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q20" s="24" t="str">
+      <c r="P20" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q20" s="27" t="str">
         <f aca="false">IF(AND(I20&lt;&gt;"",I20&gt;=0,I20&lt;=30),I20+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R20" s="24" t="n">
+      <c r="R20" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C20=Explorer!$C$4),OR(Explorer!$C$5="All",J20=Explorer!$C$5),OR(Explorer!$C$6="All",K20=Explorer!$C$6)),MAX($R$3:R19)+1,"")</f>
         <v>17</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="n">
+      <c r="A21" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="25" t="str">
+      <c r="B21" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B21,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Norway</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B21,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="D21" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B21,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B21,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Ingrid Haugen</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="31" t="n">
         <v>46428</v>
       </c>
-      <c r="I21" s="28" t="n">
+      <c r="I21" s="32" t="n">
         <f aca="true">IF(H21="","",H21-TODAY())</f>
-        <v>142</v>
-      </c>
-      <c r="J21" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="K21" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="L21" s="24" t="n">
+      <c r="K21" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L21" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="M21" s="25" t="str">
+      <c r="M21" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B21,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (University)</v>
       </c>
-      <c r="N21" s="29" t="n">
+      <c r="N21" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="27" t="n">
+      <c r="O21" s="31" t="n">
         <v>46281</v>
       </c>
-      <c r="P21" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q21" s="24" t="str">
+      <c r="P21" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q21" s="27" t="str">
         <f aca="false">IF(AND(I21&lt;&gt;"",I21&gt;=0,I21&lt;=30),I21+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R21" s="24" t="n">
+      <c r="R21" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C21=Explorer!$C$4),OR(Explorer!$C$5="All",J21=Explorer!$C$5),OR(Explorer!$C$6="All",K21=Explorer!$C$6)),MAX($R$3:R20)+1,"")</f>
         <v>18</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="n">
+      <c r="A22" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="25" t="str">
+      <c r="B22" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B22,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Canada</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" s="24" t="s">
+      <c r="D22" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="F22" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B22,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="E22" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B22,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B22,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Prof. Sarah Mitchell</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="31" t="n">
         <v>46447</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="I22" s="32" t="n">
         <f aca="true">IF(H22="","",H22-TODAY())</f>
-        <v>161</v>
-      </c>
-      <c r="J22" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="J22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="L22" s="24" t="n">
+      <c r="K22" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="M22" s="25" t="str">
+      <c r="M22" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B22,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Partially funded</v>
       </c>
-      <c r="N22" s="29" t="n">
+      <c r="N22" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O22" s="27" t="n">
+      <c r="O22" s="31" t="n">
         <v>46254</v>
       </c>
-      <c r="P22" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q22" s="24" t="str">
+      <c r="P22" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q22" s="27" t="str">
         <f aca="false">IF(AND(I22&lt;&gt;"",I22&gt;=0,I22&lt;=30),I22+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R22" s="24" t="n">
+      <c r="R22" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C22=Explorer!$C$4),OR(Explorer!$C$5="All",J22=Explorer!$C$5),OR(Explorer!$C$6="All",K22=Explorer!$C$6)),MAX($R$3:R21)+1,"")</f>
         <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="25" t="str">
+      <c r="B23" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$B$4:$B$23,MATCH(B23,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Canada</v>
       </c>
-      <c r="D23" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="24" t="s">
+      <c r="D23" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="E23" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="25" t="str">
-        <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B23,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
+      <c r="F23" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="30" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B23,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),INDEX('Universities &amp; Supervisors'!$E$4:$E$23,MATCH(B23,'Universities &amp; Supervisors'!$A$4:$A$23,0))),"")</f>
         <v>Dr. Olivier Tremblay</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="31" t="n">
         <v>46361</v>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="I23" s="32" t="n">
         <f aca="true">IF(H23="","",H23-TODAY())</f>
-        <v>75</v>
-      </c>
-      <c r="J23" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="J23" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="K23" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="L23" s="24" t="n">
+      <c r="K23" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="M23" s="25" t="str">
+      <c r="M23" s="28" t="str">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$H$4:$H$23,MATCH(B23,'Universities &amp; Supervisors'!$A$4:$A$23,0)),"")</f>
         <v>Fully funded (CIHR)</v>
       </c>
-      <c r="N23" s="29" t="n">
+      <c r="N23" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="O23" s="27" t="n">
+      <c r="O23" s="31" t="n">
         <v>46284</v>
       </c>
-      <c r="P23" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q23" s="24" t="str">
+      <c r="P23" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q23" s="27" t="str">
         <f aca="false">IF(AND(I23&lt;&gt;"",I23&gt;=0,I23&lt;=30),I23+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="R23" s="24" t="n">
+      <c r="R23" s="27" t="n">
         <f aca="false">IF(AND(OR(Explorer!$C$4="All",C23=Explorer!$C$4),OR(Explorer!$C$5="All",J23=Explorer!$C$5),OR(Explorer!$C$6="All",K23=Explorer!$C$6)),MAX($R$3:R22)+1,"")</f>
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:P23"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="O2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="I4:I53">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>0</formula>
       <formula>30</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="cellIs" priority="4" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>31</formula>
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>60</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J53">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>$J4="Accepted"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>$J4="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>$J4="Interview"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>$J4="Submitted"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>$J4="Not Started"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6079,7 +6186,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:N53">
-    <cfRule type="cellIs" priority="12" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="cellIs" priority="12" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6111,6 +6218,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="ApplyAbroadLab.com — Application Tracker Pro"/>
+    <hyperlink ref="O2" r:id="rId2" location="'Dashboard'!A1" display="◀ Back to Dashboard"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6119,7 +6227,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -6158,695 +6266,698 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
+      <c r="A2" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="23" t="s">
+      <c r="D3" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="E3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="H3" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="23" t="s">
+      <c r="G3" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="H3" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="26" t="s">
         <v>146</v>
       </c>
+      <c r="J3" s="26" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="24" t="s">
+      <c r="A4" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="24" t="s">
+      <c r="C4" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="D4" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="24" t="n">
+      <c r="G4" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="H4" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="I4" s="24" t="s">
+      <c r="H4" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="I4" s="27" t="s">
         <v>151</v>
       </c>
+      <c r="J4" s="34" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="24" t="s">
+      <c r="A5" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="24" t="s">
+      <c r="C5" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="D5" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="I5" s="24" t="s">
+      <c r="H5" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="I5" s="27" t="s">
         <v>156</v>
       </c>
+      <c r="J5" s="34" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="24" t="s">
+      <c r="A6" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="24" t="s">
+      <c r="C6" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="D6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="I6" s="24" t="s">
+      <c r="H6" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="I6" s="27" t="s">
         <v>161</v>
       </c>
+      <c r="J6" s="34" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="24" t="s">
+      <c r="A7" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="24" t="s">
+      <c r="C7" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="D7" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J7" s="30" t="s">
+      <c r="H7" s="27" t="s">
         <v>165</v>
       </c>
+      <c r="I7" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="24" t="s">
+      <c r="A8" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="24" t="s">
+      <c r="C8" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="D8" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="I8" s="24" t="s">
+      <c r="H8" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="I8" s="27" t="s">
         <v>170</v>
       </c>
+      <c r="J8" s="34" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="24" t="s">
+      <c r="A9" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="24" t="s">
+      <c r="C9" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="D9" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="H9" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>173</v>
+      <c r="H9" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="24" t="s">
+      <c r="A10" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="24" t="s">
+      <c r="C10" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="D10" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>176</v>
+      <c r="H10" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="24" t="s">
+      <c r="A11" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="24" t="s">
+      <c r="C11" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="D11" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J11" s="30" t="s">
+      <c r="H11" s="27" t="s">
         <v>180</v>
       </c>
+      <c r="I11" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="24" t="s">
+      <c r="A12" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="F12" s="24" t="n">
+      <c r="C12" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="J12" s="30" t="s">
+      <c r="H12" s="27" t="s">
         <v>183</v>
       </c>
+      <c r="I12" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="24" t="s">
+      <c r="A13" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="24" t="s">
+      <c r="C13" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="D13" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="F13" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="H13" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>186</v>
+      <c r="H13" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" s="24" t="s">
+      <c r="A14" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" s="24" t="s">
+      <c r="C14" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="D14" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F14" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="J14" s="30" t="s">
+      <c r="H14" s="27" t="s">
         <v>190</v>
       </c>
+      <c r="I14" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="24" t="s">
+      <c r="A15" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="24" t="s">
+      <c r="C15" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="D15" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J15" s="30" t="s">
+      <c r="H15" s="27" t="s">
         <v>194</v>
       </c>
+      <c r="I15" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="24" t="s">
+      <c r="C16" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="D16" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F16" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="J16" s="30" t="s">
+      <c r="H16" s="27" t="s">
         <v>198</v>
       </c>
+      <c r="I16" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="C17" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="D17" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="F17" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J17" s="30" t="s">
+      <c r="H17" s="27" t="s">
         <v>202</v>
       </c>
+      <c r="I17" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J17" s="34" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="24" t="s">
+      <c r="C18" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="D18" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="J18" s="30" t="s">
+      <c r="H18" s="27" t="s">
         <v>206</v>
       </c>
+      <c r="I18" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" s="24" t="s">
+      <c r="A19" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="24" t="s">
+      <c r="C19" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="D19" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H19" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="J19" s="30" t="s">
+      <c r="H19" s="27" t="s">
         <v>210</v>
       </c>
+      <c r="I19" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B20" s="24" t="s">
+      <c r="A20" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="24" t="s">
+      <c r="C20" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="D20" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="F20" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>213</v>
+      <c r="H20" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" s="24" t="s">
+      <c r="A21" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="24" t="s">
+      <c r="C21" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="D21" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="F21" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="G21" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="H21" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>216</v>
+      <c r="H21" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I21" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="B22" s="24" t="s">
+      <c r="A22" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="24" t="s">
+      <c r="C22" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="D22" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="F22" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G22" s="24" t="n">
+      <c r="G22" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="J22" s="30" t="s">
+      <c r="H22" s="27" t="s">
         <v>220</v>
       </c>
+      <c r="I22" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="24" t="s">
+      <c r="A23" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="24" t="s">
+      <c r="C23" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="D23" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H23" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="J23" s="30" t="s">
+      <c r="H23" s="27" t="s">
         <v>224</v>
       </c>
+      <c r="I23" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="J23" s="34" t="s">
+        <v>225</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I4:I23" type="list">
@@ -6856,26 +6967,27 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="ApplyAbroadLab.com — Application Tracker Pro"/>
-    <hyperlink ref="J4" r:id="rId2" display="https://www.tum.de"/>
-    <hyperlink ref="J5" r:id="rId3" display="https://www.uni-heidelberg.de"/>
-    <hyperlink ref="J6" r:id="rId4" display="https://www.rwth-aachen.de"/>
-    <hyperlink ref="J7" r:id="rId5" display="https://www.tudelft.nl"/>
-    <hyperlink ref="J8" r:id="rId6" display="https://www.uva.nl"/>
-    <hyperlink ref="J9" r:id="rId7" display="https://www.wur.nl"/>
-    <hyperlink ref="J10" r:id="rId8" display="https://www.uu.nl"/>
-    <hyperlink ref="J11" r:id="rId9" display="https://ki.se"/>
-    <hyperlink ref="J12" r:id="rId10" display="https://www.kth.se"/>
-    <hyperlink ref="J13" r:id="rId11" display="https://www.lu.se"/>
-    <hyperlink ref="J14" r:id="rId12" display="https://www.polimi.it"/>
-    <hyperlink ref="J15" r:id="rId13" display="https://www.unibo.it"/>
-    <hyperlink ref="J16" r:id="rId14" display="https://www.kuleuven.be"/>
-    <hyperlink ref="J17" r:id="rId15" display="https://www.ugent.be"/>
-    <hyperlink ref="J18" r:id="rId16" display="https://ethz.ch"/>
-    <hyperlink ref="J19" r:id="rId17" display="https://www.epfl.ch"/>
-    <hyperlink ref="J20" r:id="rId18" display="https://www.ntnu.edu"/>
-    <hyperlink ref="J21" r:id="rId19" display="https://www.uio.no"/>
-    <hyperlink ref="J22" r:id="rId20" display="https://www.utoronto.ca"/>
-    <hyperlink ref="J23" r:id="rId21" display="https://www.mcgill.ca"/>
+    <hyperlink ref="I2" r:id="rId2" location="'Dashboard'!A1" display="◀ Back to Dashboard"/>
+    <hyperlink ref="J4" r:id="rId3" display="https://www.tum.de"/>
+    <hyperlink ref="J5" r:id="rId4" display="https://www.uni-heidelberg.de"/>
+    <hyperlink ref="J6" r:id="rId5" display="https://www.rwth-aachen.de"/>
+    <hyperlink ref="J7" r:id="rId6" display="https://www.tudelft.nl"/>
+    <hyperlink ref="J8" r:id="rId7" display="https://www.uva.nl"/>
+    <hyperlink ref="J9" r:id="rId8" display="https://www.wur.nl"/>
+    <hyperlink ref="J10" r:id="rId9" display="https://www.uu.nl"/>
+    <hyperlink ref="J11" r:id="rId10" display="https://ki.se"/>
+    <hyperlink ref="J12" r:id="rId11" display="https://www.kth.se"/>
+    <hyperlink ref="J13" r:id="rId12" display="https://www.lu.se"/>
+    <hyperlink ref="J14" r:id="rId13" display="https://www.polimi.it"/>
+    <hyperlink ref="J15" r:id="rId14" display="https://www.unibo.it"/>
+    <hyperlink ref="J16" r:id="rId15" display="https://www.kuleuven.be"/>
+    <hyperlink ref="J17" r:id="rId16" display="https://www.ugent.be"/>
+    <hyperlink ref="J18" r:id="rId17" display="https://ethz.ch"/>
+    <hyperlink ref="J19" r:id="rId18" display="https://www.epfl.ch"/>
+    <hyperlink ref="J20" r:id="rId19" display="https://www.ntnu.edu"/>
+    <hyperlink ref="J21" r:id="rId20" display="https://www.uio.no"/>
+    <hyperlink ref="J22" r:id="rId21" display="https://www.utoronto.ca"/>
+    <hyperlink ref="J23" r:id="rId22" display="https://www.mcgill.ca"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6918,827 +7030,830 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" s="31" t="s">
+      <c r="C4" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="E4" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" s="37" t="n">
         <f aca="false">COUNT(Applications!R4:R23)</f>
         <v>20</v>
       </c>
-      <c r="G4" s="33"/>
+      <c r="G4" s="37"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="F5" s="33" t="n">
+      <c r="C5" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" s="37" t="n">
         <f aca="false">IFERROR(ROUND(SUMPRODUCT((Applications!R4:R23&lt;&gt;"")*Applications!L4:L23)/$F$4,1),0)</f>
         <v>7.7</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="37"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="F6" s="34" t="n">
+      <c r="B6" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" s="38" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Applications!R4:R23&lt;&gt;"")*Applications!N4:N23)/$F$4,0)</f>
         <v>0.6425</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="38"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="F7" s="33" t="n">
+      <c r="E7" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="37" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(MIN(IF(Applications!R4:R23&lt;&gt;"",IF(Applications!I4:I23&gt;=0,Applications!I4:I23)))),"")</f>
-        <v>14</v>
-      </c>
-      <c r="G7" s="33"/>
+        <v>13</v>
+      </c>
+      <c r="G7" s="37"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>55</v>
+      <c r="H9" s="26" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="n">
+      <c r="A10" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A10,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B10" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A10,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A10,Applications!$R$4:$R$23,0))),"")</f>
         <v>Technical University of Munich</v>
       </c>
-      <c r="C10" s="24" t="str">
+      <c r="C10" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A10,Applications!$R$4:$R$23,0)),"")</f>
         <v>Germany</v>
       </c>
-      <c r="D10" s="26" t="str">
+      <c r="D10" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A10,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Computational Biology</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A10,Applications!$R$4:$R$23,0)),"")</f>
         <v>46300</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A10,Applications!$R$4:$R$23,0)),"")</f>
-        <v>14</v>
-      </c>
-      <c r="G10" s="24" t="str">
+        <v>13</v>
+      </c>
+      <c r="G10" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A10,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H10" s="24" t="str">
+      <c r="H10" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A10,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A11,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B11" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A11,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A11,Applications!$R$4:$R$23,0))),"")</f>
         <v>Heidelberg University</v>
       </c>
-      <c r="C11" s="24" t="str">
+      <c r="C11" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A11,Applications!$R$4:$R$23,0)),"")</f>
         <v>Germany</v>
       </c>
-      <c r="D11" s="26" t="str">
+      <c r="D11" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A11,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Molecular Oncology (DKFZ)</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A11,Applications!$R$4:$R$23,0)),"")</f>
         <v>46341</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A11,Applications!$R$4:$R$23,0)),"")</f>
-        <v>55</v>
-      </c>
-      <c r="G11" s="24" t="str">
+        <v>54</v>
+      </c>
+      <c r="G11" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A11,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H11" s="24" t="str">
+      <c r="H11" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A11,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="n">
+      <c r="A12" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A12,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B12" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A12,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A12,Applications!$R$4:$R$23,0))),"")</f>
         <v>RWTH Aachen University</v>
       </c>
-      <c r="C12" s="24" t="str">
+      <c r="C12" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A12,Applications!$R$4:$R$23,0)),"")</f>
         <v>Germany</v>
       </c>
-      <c r="D12" s="26" t="str">
+      <c r="D12" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A12,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Mechanical Engineering</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A12,Applications!$R$4:$R$23,0)),"")</f>
         <v>46418</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A12,Applications!$R$4:$R$23,0)),"")</f>
-        <v>132</v>
-      </c>
-      <c r="G12" s="24" t="str">
+        <v>131</v>
+      </c>
+      <c r="G12" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A12,Applications!$R$4:$R$23,0)),"")</f>
         <v>Not Started</v>
       </c>
-      <c r="H12" s="24" t="str">
+      <c r="H12" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A12,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A13,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B13" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A13,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A13,Applications!$R$4:$R$23,0))),"")</f>
         <v>Delft University of Technology</v>
       </c>
-      <c r="C13" s="24" t="str">
+      <c r="C13" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A13,Applications!$R$4:$R$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D13" s="26" t="str">
+      <c r="D13" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A13,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Structural Engineering</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A13,Applications!$R$4:$R$23,0)),"")</f>
         <v>46307</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A13,Applications!$R$4:$R$23,0)),"")</f>
-        <v>21</v>
-      </c>
-      <c r="G13" s="24" t="str">
+        <v>20</v>
+      </c>
+      <c r="G13" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A13,Applications!$R$4:$R$23,0)),"")</f>
         <v>Submitted</v>
       </c>
-      <c r="H13" s="24" t="str">
+      <c r="H13" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A13,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A14,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B14" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A14,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A14,Applications!$R$4:$R$23,0))),"")</f>
         <v>University of Amsterdam</v>
       </c>
-      <c r="C14" s="24" t="str">
+      <c r="C14" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A14,Applications!$R$4:$R$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D14" s="26" t="str">
+      <c r="D14" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A14,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Clinical Psychology</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A14,Applications!$R$4:$R$23,0)),"")</f>
         <v>46313</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A14,Applications!$R$4:$R$23,0)),"")</f>
-        <v>27</v>
-      </c>
-      <c r="G14" s="24" t="str">
+        <v>26</v>
+      </c>
+      <c r="G14" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A14,Applications!$R$4:$R$23,0)),"")</f>
         <v>Interview</v>
       </c>
-      <c r="H14" s="24" t="str">
+      <c r="H14" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A14,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A15,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B15" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A15,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A15,Applications!$R$4:$R$23,0))),"")</f>
         <v>Wageningen University</v>
       </c>
-      <c r="C15" s="24" t="str">
+      <c r="C15" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A15,Applications!$R$4:$R$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D15" s="26" t="str">
+      <c r="D15" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A15,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Food Biotechnology</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A15,Applications!$R$4:$R$23,0)),"")</f>
         <v>46357</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A15,Applications!$R$4:$R$23,0)),"")</f>
-        <v>71</v>
-      </c>
-      <c r="G15" s="24" t="str">
+        <v>70</v>
+      </c>
+      <c r="G15" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A15,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H15" s="24" t="str">
+      <c r="H15" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A15,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A16,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B16" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A16,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A16,Applications!$R$4:$R$23,0))),"")</f>
         <v>Utrecht University</v>
       </c>
-      <c r="C16" s="24" t="str">
+      <c r="C16" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A16,Applications!$R$4:$R$23,0)),"")</f>
         <v>Netherlands</v>
       </c>
-      <c r="D16" s="26" t="str">
+      <c r="D16" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A16,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Developmental Biology</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A16,Applications!$R$4:$R$23,0)),"")</f>
         <v>46371</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A16,Applications!$R$4:$R$23,0)),"")</f>
-        <v>85</v>
-      </c>
-      <c r="G16" s="24" t="str">
+        <v>84</v>
+      </c>
+      <c r="G16" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A16,Applications!$R$4:$R$23,0)),"")</f>
         <v>Not Started</v>
       </c>
-      <c r="H16" s="24" t="str">
+      <c r="H16" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A16,Applications!$R$4:$R$23,0)),"")</f>
         <v>Low</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A17,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B17" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A17,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A17,Applications!$R$4:$R$23,0))),"")</f>
         <v>Karolinska Institutet</v>
       </c>
-      <c r="C17" s="24" t="str">
+      <c r="C17" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A17,Applications!$R$4:$R$23,0)),"")</f>
         <v>Sweden</v>
       </c>
-      <c r="D17" s="26" t="str">
+      <c r="D17" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A17,Applications!$R$4:$R$23,0)),"")</f>
         <v>Postdoc in Cancer Biology</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A17,Applications!$R$4:$R$23,0)),"")</f>
         <v>46315</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A17,Applications!$R$4:$R$23,0)),"")</f>
-        <v>29</v>
-      </c>
-      <c r="G17" s="24" t="str">
+        <v>28</v>
+      </c>
+      <c r="G17" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A17,Applications!$R$4:$R$23,0)),"")</f>
         <v>Submitted</v>
       </c>
-      <c r="H17" s="24" t="str">
+      <c r="H17" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A17,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A18,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B18" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A18,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A18,Applications!$R$4:$R$23,0))),"")</f>
         <v>KTH Royal Institute of Technology</v>
       </c>
-      <c r="C18" s="24" t="str">
+      <c r="C18" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A18,Applications!$R$4:$R$23,0)),"")</f>
         <v>Sweden</v>
       </c>
-      <c r="D18" s="26" t="str">
+      <c r="D18" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A18,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Machine Learning (WASP)</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A18,Applications!$R$4:$R$23,0)),"")</f>
         <v>46356</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A18,Applications!$R$4:$R$23,0)),"")</f>
-        <v>70</v>
-      </c>
-      <c r="G18" s="24" t="str">
+        <v>69</v>
+      </c>
+      <c r="G18" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A18,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H18" s="24" t="str">
+      <c r="H18" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A18,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A19,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B19" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A19,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A19,Applications!$R$4:$R$23,0))),"")</f>
         <v>Lund University</v>
       </c>
-      <c r="C19" s="24" t="str">
+      <c r="C19" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A19,Applications!$R$4:$R$23,0)),"")</f>
         <v>Sweden</v>
       </c>
-      <c r="D19" s="26" t="str">
+      <c r="D19" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A19,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Analytical Chemistry</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A19,Applications!$R$4:$R$23,0)),"")</f>
         <v>46402</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A19,Applications!$R$4:$R$23,0)),"")</f>
-        <v>116</v>
-      </c>
-      <c r="G19" s="24" t="str">
+        <v>115</v>
+      </c>
+      <c r="G19" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A19,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H19" s="24" t="str">
+      <c r="H19" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A19,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="n">
+      <c r="A20" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A20,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B20" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A20,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A20,Applications!$R$4:$R$23,0))),"")</f>
         <v>Politecnico di Milano</v>
       </c>
-      <c r="C20" s="24" t="str">
+      <c r="C20" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A20,Applications!$R$4:$R$23,0)),"")</f>
         <v>Italy</v>
       </c>
-      <c r="D20" s="26" t="str">
+      <c r="D20" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A20,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Architecture &amp; Urban Design</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A20,Applications!$R$4:$R$23,0)),"")</f>
         <v>46446</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A20,Applications!$R$4:$R$23,0)),"")</f>
-        <v>160</v>
-      </c>
-      <c r="G20" s="24" t="str">
+        <v>159</v>
+      </c>
+      <c r="G20" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A20,Applications!$R$4:$R$23,0)),"")</f>
         <v>Not Started</v>
       </c>
-      <c r="H20" s="24" t="str">
+      <c r="H20" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A20,Applications!$R$4:$R$23,0)),"")</f>
         <v>Low</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="n">
+      <c r="A21" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A21,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B21" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A21,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A21,Applications!$R$4:$R$23,0))),"")</f>
         <v>University of Bologna</v>
       </c>
-      <c r="C21" s="24" t="str">
+      <c r="C21" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A21,Applications!$R$4:$R$23,0)),"")</f>
         <v>Italy</v>
       </c>
-      <c r="D21" s="26" t="str">
+      <c r="D21" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A21,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Management</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A21,Applications!$R$4:$R$23,0)),"")</f>
         <v>46461</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A21,Applications!$R$4:$R$23,0)),"")</f>
-        <v>175</v>
-      </c>
-      <c r="G21" s="24" t="str">
+        <v>174</v>
+      </c>
+      <c r="G21" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A21,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H21" s="24" t="str">
+      <c r="H21" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A21,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="n">
+      <c r="A22" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A22,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B22" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A22,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A22,Applications!$R$4:$R$23,0))),"")</f>
         <v>KU Leuven</v>
       </c>
-      <c r="C22" s="24" t="str">
+      <c r="C22" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A22,Applications!$R$4:$R$23,0)),"")</f>
         <v>Belgium</v>
       </c>
-      <c r="D22" s="26" t="str">
+      <c r="D22" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A22,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Organic Chemistry</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A22,Applications!$R$4:$R$23,0)),"")</f>
         <v>46336</v>
       </c>
-      <c r="F22" s="35" t="n">
+      <c r="F22" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A22,Applications!$R$4:$R$23,0)),"")</f>
-        <v>50</v>
-      </c>
-      <c r="G22" s="24" t="str">
+        <v>49</v>
+      </c>
+      <c r="G22" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A22,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H22" s="24" t="str">
+      <c r="H22" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A22,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A23,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B23" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A23,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A23,Applications!$R$4:$R$23,0))),"")</f>
         <v>Ghent University</v>
       </c>
-      <c r="C23" s="24" t="str">
+      <c r="C23" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A23,Applications!$R$4:$R$23,0)),"")</f>
         <v>Belgium</v>
       </c>
-      <c r="D23" s="26" t="str">
+      <c r="D23" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A23,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Plant Biology</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A23,Applications!$R$4:$R$23,0)),"")</f>
         <v>46376</v>
       </c>
-      <c r="F23" s="35" t="n">
+      <c r="F23" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A23,Applications!$R$4:$R$23,0)),"")</f>
-        <v>90</v>
-      </c>
-      <c r="G23" s="24" t="str">
+        <v>89</v>
+      </c>
+      <c r="G23" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A23,Applications!$R$4:$R$23,0)),"")</f>
         <v>Submitted</v>
       </c>
-      <c r="H23" s="24" t="str">
+      <c r="H23" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A23,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="n">
+      <c r="A24" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A24,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B24" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A24,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A24,Applications!$R$4:$R$23,0))),"")</f>
         <v>ETH Zurich</v>
       </c>
-      <c r="C24" s="24" t="str">
+      <c r="C24" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A24,Applications!$R$4:$R$23,0)),"")</f>
         <v>Switzerland</v>
       </c>
-      <c r="D24" s="26" t="str">
+      <c r="D24" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A24,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Computer Science</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A24,Applications!$R$4:$R$23,0)),"")</f>
         <v>46366</v>
       </c>
-      <c r="F24" s="35" t="n">
+      <c r="F24" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A24,Applications!$R$4:$R$23,0)),"")</f>
-        <v>80</v>
-      </c>
-      <c r="G24" s="24" t="str">
+        <v>79</v>
+      </c>
+      <c r="G24" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A24,Applications!$R$4:$R$23,0)),"")</f>
         <v>Not Started</v>
       </c>
-      <c r="H24" s="24" t="str">
+      <c r="H24" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A24,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="n">
+      <c r="A25" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A25,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B25" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A25,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A25,Applications!$R$4:$R$23,0))),"")</f>
         <v>EPFL</v>
       </c>
-      <c r="C25" s="24" t="str">
+      <c r="C25" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A25,Applications!$R$4:$R$23,0)),"")</f>
         <v>Switzerland</v>
       </c>
-      <c r="D25" s="26" t="str">
+      <c r="D25" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A25,Applications!$R$4:$R$23,0)),"")</f>
         <v>Postdoc in Robotics</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A25,Applications!$R$4:$R$23,0)),"")</f>
         <v>46407</v>
       </c>
-      <c r="F25" s="35" t="n">
+      <c r="F25" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A25,Applications!$R$4:$R$23,0)),"")</f>
-        <v>121</v>
-      </c>
-      <c r="G25" s="24" t="str">
+        <v>120</v>
+      </c>
+      <c r="G25" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A25,Applications!$R$4:$R$23,0)),"")</f>
         <v>In Progress</v>
       </c>
-      <c r="H25" s="24" t="str">
+      <c r="H25" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A25,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="n">
+      <c r="A26" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B26" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A26,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B26" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A26,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A26,Applications!$R$4:$R$23,0))),"")</f>
         <v>NTNU</v>
       </c>
-      <c r="C26" s="24" t="str">
+      <c r="C26" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A26,Applications!$R$4:$R$23,0)),"")</f>
         <v>Norway</v>
       </c>
-      <c r="D26" s="26" t="str">
+      <c r="D26" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A26,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Geotechnical Engineering</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A26,Applications!$R$4:$R$23,0)),"")</f>
         <v>46351</v>
       </c>
-      <c r="F26" s="35" t="n">
+      <c r="F26" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A26,Applications!$R$4:$R$23,0)),"")</f>
-        <v>65</v>
-      </c>
-      <c r="G26" s="24" t="str">
+        <v>64</v>
+      </c>
+      <c r="G26" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A26,Applications!$R$4:$R$23,0)),"")</f>
         <v>Interview</v>
       </c>
-      <c r="H26" s="24" t="str">
+      <c r="H26" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A26,Applications!$R$4:$R$23,0)),"")</f>
         <v>High</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="n">
+      <c r="A27" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B27" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A27,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B27" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A27,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A27,Applications!$R$4:$R$23,0))),"")</f>
         <v>University of Oslo</v>
       </c>
-      <c r="C27" s="24" t="str">
+      <c r="C27" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A27,Applications!$R$4:$R$23,0)),"")</f>
         <v>Norway</v>
       </c>
-      <c r="D27" s="26" t="str">
+      <c r="D27" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A27,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Cognitive Psychology</v>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A27,Applications!$R$4:$R$23,0)),"")</f>
         <v>46428</v>
       </c>
-      <c r="F27" s="35" t="n">
+      <c r="F27" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A27,Applications!$R$4:$R$23,0)),"")</f>
-        <v>142</v>
-      </c>
-      <c r="G27" s="24" t="str">
+        <v>141</v>
+      </c>
+      <c r="G27" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A27,Applications!$R$4:$R$23,0)),"")</f>
         <v>Interview</v>
       </c>
-      <c r="H27" s="24" t="str">
+      <c r="H27" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A27,Applications!$R$4:$R$23,0)),"")</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="n">
+      <c r="A28" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A28,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B28" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A28,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A28,Applications!$R$4:$R$23,0))),"")</f>
         <v>University of Toronto</v>
       </c>
-      <c r="C28" s="24" t="str">
+      <c r="C28" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A28,Applications!$R$4:$R$23,0)),"")</f>
         <v>Canada</v>
       </c>
-      <c r="D28" s="26" t="str">
+      <c r="D28" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A28,Applications!$R$4:$R$23,0)),"")</f>
         <v>PhD in Marketing</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A28,Applications!$R$4:$R$23,0)),"")</f>
         <v>46447</v>
       </c>
-      <c r="F28" s="35" t="n">
+      <c r="F28" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A28,Applications!$R$4:$R$23,0)),"")</f>
-        <v>161</v>
-      </c>
-      <c r="G28" s="24" t="str">
+        <v>160</v>
+      </c>
+      <c r="G28" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A28,Applications!$R$4:$R$23,0)),"")</f>
         <v>Rejected</v>
       </c>
-      <c r="H28" s="24" t="str">
+      <c r="H28" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A28,Applications!$R$4:$R$23,0)),"")</f>
         <v>Low</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="n">
+      <c r="A29" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="24" t="str">
-        <f aca="false">IFERROR(INDEX(Applications!$B$4:$B$23,MATCH($A29,Applications!$R$4:$R$23,0)),"")</f>
+      <c r="B29" s="39" t="str">
+        <f aca="false">IFERROR(HYPERLINK("#'Applications'!A"&amp;(MATCH($A29,Applications!$R$4:$R$23,0)+3),INDEX(Applications!$B$4:$B$23,MATCH($A29,Applications!$R$4:$R$23,0))),"")</f>
         <v>McGill University</v>
       </c>
-      <c r="C29" s="24" t="str">
+      <c r="C29" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$C$4:$C$23,MATCH($A29,Applications!$R$4:$R$23,0)),"")</f>
         <v>Canada</v>
       </c>
-      <c r="D29" s="26" t="str">
+      <c r="D29" s="29" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$D$4:$D$23,MATCH($A29,Applications!$R$4:$R$23,0)),"")</f>
         <v>Postdoc in Cancer Biology</v>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="31" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$H$4:$H$23,MATCH($A29,Applications!$R$4:$R$23,0)),"")</f>
         <v>46361</v>
       </c>
-      <c r="F29" s="35" t="n">
+      <c r="F29" s="40" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$I$4:$I$23,MATCH($A29,Applications!$R$4:$R$23,0)),"")</f>
-        <v>75</v>
-      </c>
-      <c r="G29" s="24" t="str">
+        <v>74</v>
+      </c>
+      <c r="G29" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$J$4:$J$23,MATCH($A29,Applications!$R$4:$R$23,0)),"")</f>
         <v>Accepted</v>
       </c>
-      <c r="H29" s="24" t="str">
+      <c r="H29" s="27" t="str">
         <f aca="false">IFERROR(INDEX(Applications!$K$4:$K$23,MATCH($A29,Applications!$R$4:$R$23,0)),"")</f>
         <v>Low</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="C31" s="36" t="s">
+      <c r="B31" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="C31" s="41" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="37" t="n">
+      <c r="C32" s="42" t="n">
         <f aca="false">SUMPRODUCT((Applications!$R$4:$R$23&lt;&gt;"")*(Applications!$J$4:$J$23="Not Started"))</f>
         <v>4</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="37" t="n">
+      <c r="C33" s="42" t="n">
         <f aca="false">SUMPRODUCT((Applications!$R$4:$R$23&lt;&gt;"")*(Applications!$J$4:$J$23="In Progress"))</f>
         <v>8</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="37" t="n">
+      <c r="C34" s="42" t="n">
         <f aca="false">SUMPRODUCT((Applications!$R$4:$R$23&lt;&gt;"")*(Applications!$J$4:$J$23="Submitted"))</f>
         <v>3</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="37" t="n">
+      <c r="C35" s="42" t="n">
         <f aca="false">SUMPRODUCT((Applications!$R$4:$R$23&lt;&gt;"")*(Applications!$J$4:$J$23="Interview"))</f>
         <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="37" t="n">
+      <c r="C36" s="42" t="n">
         <f aca="false">SUMPRODUCT((Applications!$R$4:$R$23&lt;&gt;"")*(Applications!$J$4:$J$23="Accepted"))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="37" t="n">
+      <c r="C37" s="42" t="n">
         <f aca="false">SUMPRODUCT((Applications!$R$4:$R$23&lt;&gt;"")*(Applications!$J$4:$J$23="Rejected"))</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:H2"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F6:G6"/>
@@ -7749,7 +7864,7 @@
       <formula>0</formula>
       <formula>30</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
       <formula>31</formula>
       <formula>60</formula>
     </cfRule>
@@ -7775,6 +7890,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="ApplyAbroadLab.com — Application Tracker Pro"/>
+    <hyperlink ref="G2" r:id="rId2" location="'Dashboard'!A1" display="◀ Back to Dashboard"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7783,7 +7899,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -7792,7 +7908,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="26"/>
@@ -7814,206 +7930,229 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="G2" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" s="23" t="s">
+      <c r="A3" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="B3" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23" t="s">
+      <c r="E3" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="H3" s="23"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="H3" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>122</v>
+      <c r="B4" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="24" t="n">
+      <c r="A5" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="27" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$L$4:$L$23,MATCH(B$4,Applications!$B$4:$B$23,0)),0)</f>
         <v>9</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="27" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$L$4:$L$23,MATCH(C$4,Applications!$B$4:$B$23,0)),0)</f>
         <v>9</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="27" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$L$4:$L$23,MATCH(D$4,Applications!$B$4:$B$23,0)),0)</f>
         <v>7</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="27" t="n">
         <f aca="false">IFERROR(INDEX(Applications!$L$4:$L$23,MATCH(E$4,Applications!$B$4:$B$23,0)),0)</f>
         <v>9</v>
       </c>
-      <c r="G5" s="39" t="s">
-        <v>240</v>
-      </c>
-      <c r="H5" s="39"/>
+      <c r="G5" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="24" t="n">
+      <c r="A6" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="27" t="n">
         <f aca="false">IFERROR(IF(ISNUMBER(SEARCH("Fully",INDEX(Applications!$M$4:$M$23,MATCH(B$4,Applications!$B$4:$B$23,0)))),10,IF(ISNUMBER(SEARCH("Partial",INDEX(Applications!$M$4:$M$23,MATCH(B$4,Applications!$B$4:$B$23,0)))),6,7)),0)</f>
         <v>10</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="27" t="n">
         <f aca="false">IFERROR(IF(ISNUMBER(SEARCH("Fully",INDEX(Applications!$M$4:$M$23,MATCH(C$4,Applications!$B$4:$B$23,0)))),10,IF(ISNUMBER(SEARCH("Partial",INDEX(Applications!$M$4:$M$23,MATCH(C$4,Applications!$B$4:$B$23,0)))),6,7)),0)</f>
         <v>10</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="27" t="n">
         <f aca="false">IFERROR(IF(ISNUMBER(SEARCH("Fully",INDEX(Applications!$M$4:$M$23,MATCH(D$4,Applications!$B$4:$B$23,0)))),10,IF(ISNUMBER(SEARCH("Partial",INDEX(Applications!$M$4:$M$23,MATCH(D$4,Applications!$B$4:$B$23,0)))),6,7)),0)</f>
         <v>7</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="27" t="n">
         <f aca="false">IFERROR(IF(ISNUMBER(SEARCH("Fully",INDEX(Applications!$M$4:$M$23,MATCH(E$4,Applications!$B$4:$B$23,0)))),10,IF(ISNUMBER(SEARCH("Partial",INDEX(Applications!$M$4:$M$23,MATCH(E$4,Applications!$B$4:$B$23,0)))),6,7)),0)</f>
         <v>10</v>
       </c>
-      <c r="G6" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="H6" s="39"/>
+      <c r="G6" s="44" t="s">
+        <v>243</v>
+      </c>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="24" t="n">
+      <c r="A7" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$F$4:$F$23,MATCH(B$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>9</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$F$4:$F$23,MATCH(C$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>10</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$F$4:$F$23,MATCH(D$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>7</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$F$4:$F$23,MATCH(E$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>10</v>
       </c>
-      <c r="G7" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="H7" s="39"/>
+      <c r="G7" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="H7" s="44"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="B8" s="24" t="n">
+      <c r="A8" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,MIN(10,ROUND(10-INDEX(Applications!$I$4:$I$23,MATCH(B$4,Applications!$B$4:$B$23,0))/20,0))),0)</f>
         <v>9</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,MIN(10,ROUND(10-INDEX(Applications!$I$4:$I$23,MATCH(C$4,Applications!$B$4:$B$23,0))/20,0))),0)</f>
         <v>9</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,MIN(10,ROUND(10-INDEX(Applications!$I$4:$I$23,MATCH(D$4,Applications!$B$4:$B$23,0))/20,0))),0)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,MIN(10,ROUND(10-INDEX(Applications!$I$4:$I$23,MATCH(E$4,Applications!$B$4:$B$23,0))/20,0))),0)</f>
         <v>6</v>
       </c>
-      <c r="G8" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="H8" s="39"/>
+      <c r="G8" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="H8" s="44"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="B9" s="24" t="n">
+      <c r="A9" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$G$4:$G$23,MATCH(B$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$G$4:$G$23,MATCH(C$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>6</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$G$4:$G$23,MATCH(D$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>6</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="27" t="n">
         <f aca="false">IFERROR(INDEX('Universities &amp; Supervisors'!$G$4:$G$23,MATCH(E$4,'Universities &amp; Supervisors'!$A$4:$A$23,0)),0)</f>
         <v>4</v>
       </c>
-      <c r="G9" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="H9" s="39"/>
+      <c r="G9" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" s="31" t="n">
+      <c r="A10" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B10" s="35" t="n">
         <f aca="false">ROUND(AVERAGE(B5:B9),1)</f>
         <v>8.8</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="35" t="n">
         <f aca="false">ROUND(AVERAGE(C5:C9),1)</f>
         <v>8.8</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="35" t="n">
         <f aca="false">ROUND(AVERAGE(D5:D9),1)</f>
         <v>5.6</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="35" t="n">
         <f aca="false">ROUND(AVERAGE(E5:E9),1)</f>
         <v>7.8</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="B11" s="46" t="str">
+        <f aca="false">IF(B4="","",HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(B4,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),"Open ▸"))</f>
+        <v>Open ▸</v>
+      </c>
+      <c r="C11" s="46" t="str">
+        <f aca="false">IF(C4="","",HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(C4,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),"Open ▸"))</f>
+        <v>Open ▸</v>
+      </c>
+      <c r="D11" s="46" t="str">
+        <f aca="false">IF(D4="","",HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(D4,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),"Open ▸"))</f>
+        <v>Open ▸</v>
+      </c>
+      <c r="E11" s="46" t="str">
+        <f aca="false">IF(E4="","",HYPERLINK("#'Universities &amp; Supervisors'!A"&amp;(MATCH(E4,'Universities &amp; Supervisors'!$A$4:$A$23,0)+3),"Open ▸"))</f>
+        <v>Open ▸</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H6"/>
@@ -8029,6 +8168,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="ApplyAbroadLab.com — Application Tracker Pro"/>
+    <hyperlink ref="G2" r:id="rId2" location="'Dashboard'!A1" display="◀ Back to Dashboard"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8037,7 +8177,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -8046,7 +8186,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -8065,88 +8205,99 @@
       <c r="F1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="40" t="s">
-        <v>250</v>
+      <c r="B3" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>252</v>
+      <c r="B5" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>254</v>
+      <c r="B6" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="41" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>256</v>
+      <c r="B7" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="41" t="s">
-        <v>257</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>258</v>
+      <c r="B8" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>260</v>
+      <c r="B9" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>262</v>
+      <c r="B10" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="41" t="s">
-        <v>263</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>264</v>
+      <c r="B11" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>266</v>
+      <c r="B12" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>268</v>
+      <c r="B13" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>270</v>
+      <c r="B14" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -8155,6 +8306,13 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="ApplyAbroadLab.com — Application Tracker Pro"/>
+    <hyperlink ref="C3" r:id="rId2" location="'Dashboard'!A1" display="◀ Back to Dashboard"/>
+    <hyperlink ref="B6" r:id="rId3" location="'Applications'!A1" display="Data model"/>
+    <hyperlink ref="B7" r:id="rId4" location="'Dashboard'!A1" display="What is automated"/>
+    <hyperlink ref="B8" r:id="rId5" location="'Applications'!A1" display="Adding an application"/>
+    <hyperlink ref="B9" r:id="rId6" location="'Universities%20&amp;%20Supervisors'!A1" display="Adding a university"/>
+    <hyperlink ref="B10" r:id="rId7" location="'Scoring'!A1" display="Comparing a shortlist"/>
+    <hyperlink ref="B11" r:id="rId8" location="'Explorer'!A1" display="Filtering"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8178,29 +8336,29 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="36" t="s">
+      <c r="B1" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="G1" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="I1" s="36" t="s">
-        <v>273</v>
+      <c r="E1" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1" s="41" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8208,25 +8366,25 @@
         <v>11</v>
       </c>
       <c r="B2" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>66</v>
-      </c>
       <c r="D2" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8234,16 +8392,16 @@
         <v>12</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>97</v>
-      </c>
       <c r="E3" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>21</v>
@@ -8252,7 +8410,7 @@
         <v>11</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8260,16 +8418,16 @@
         <v>16</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>22</v>
@@ -8278,7 +8436,7 @@
         <v>12</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8286,10 +8444,10 @@
         <v>17</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>23</v>
@@ -8298,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8306,7 +8464,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>24</v>
@@ -8320,7 +8478,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>25</v>
@@ -8331,7 +8489,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>26</v>
@@ -8342,7 +8500,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>27</v>
@@ -8350,7 +8508,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>28</v>
@@ -8358,22 +8516,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
